--- a/test/inputs/issue34.xlsx
+++ b/test/inputs/issue34.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qr24461/.julia/dev/esm/test/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{146977A4-3FB3-9948-84ED-BDD18FD726E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1515792-D251-8042-8C33-0598744A2BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="1740" windowWidth="18980" windowHeight="9440" xr2:uid="{7C37CC98-1F4A-4A36-93A3-A48642CDB423}"/>
+    <workbookView xWindow="-30240" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{7C37CC98-1F4A-4A36-93A3-A48642CDB423}"/>
   </bookViews>
   <sheets>
     <sheet name="Samples" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Plate</t>
   </si>
@@ -69,34 +69,28 @@
     <t>Plate reader</t>
   </si>
   <si>
-    <t>biotek</t>
-  </si>
-  <si>
-    <t>$GITHUB_WORKSPACE/test/inputs/biotek-data.csv</t>
+    <t>od1</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>New name</t>
+  </si>
+  <si>
+    <t>Samples</t>
+  </si>
+  <si>
+    <t>View</t>
   </si>
   <si>
     <t>600</t>
   </si>
   <si>
-    <t>od1</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>od2</t>
-  </si>
-  <si>
-    <t>Channel</t>
-  </si>
-  <si>
-    <t>New name</t>
-  </si>
-  <si>
-    <t>Samples</t>
-  </si>
-  <si>
-    <t>View</t>
+    <t>spectramax</t>
+  </si>
+  <si>
+    <t>$GITHUB_WORKSPACE/test/inputs/spectramax-data.txt</t>
   </si>
 </sst>
 </file>
@@ -513,13 +507,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2">
-        <v>600</v>
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -541,27 +535,22 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -584,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -624,7 +613,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
